--- a/02_DIA_inicio_2026_analisis_assets/rbd_9710_escuela-basica-santa-adriana_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9710_escuela-basica-santa-adriana_nt2_rubricas.xlsx
@@ -1956,13 +1956,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4B34305-F7CA-4326-ADB7-3EC30FD738CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87309441-0D12-45F7-898D-AF4CF3B8AF14}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FC6B116-A76C-4308-A5F3-7043704A0C15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8AE2688-B3A7-4272-8F43-BC3B9D8236AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC168340-14A4-49EC-9AA3-1F6257D2582A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7C31CC2-2923-490D-BE80-136FC0DFE6E0}"/>
 </file>